--- a/Top 7 broker List with its Turnover 2022-12-11.xlsx
+++ b/Top 7 broker List with its Turnover 2022-12-11.xlsx
@@ -167,7 +167,7 @@
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>270,038,710.3</t>
+    <t>279,619,989.6</t>
   </si>
   <si>
     <t>Hydro Power</t>
@@ -185,7 +185,7 @@
     <t>Microfinance</t>
   </si>
   <si>
-    <t>146,625,369.4</t>
+    <t>135,817,404.69</t>
   </si>
   <si>
     <t>Development Banks</t>
@@ -194,16 +194,16 @@
     <t>59,011,000.7</t>
   </si>
   <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>45,013,662.4</t>
+  </si>
+  <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>47,622,645.2</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>45,013,662.4</t>
+    <t>44,847,119.5</t>
   </si>
   <si>
     <t>Investment</t>
@@ -227,7 +227,7 @@
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>14,769,686.1</t>
+    <t>18,771,897.2</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
@@ -1199,7 +1199,7 @@
         <v>50</v>
       </c>
       <c r="D31" s="12">
-        <v>0.2447323910983319</v>
+        <v>0.2534157735299283</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1232,7 +1232,7 @@
         <v>56</v>
       </c>
       <c r="D34" s="12">
-        <v>0.1328845675831914</v>
+        <v>0.123089456945169</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -1254,7 +1254,7 @@
         <v>60</v>
       </c>
       <c r="D36" s="12">
-        <v>0.04315975223432068</v>
+        <v>0.04079526679344046</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -1265,7 +1265,7 @@
         <v>62</v>
       </c>
       <c r="D37" s="12">
-        <v>0.04079526679344046</v>
+        <v>0.04064433124019267</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -1309,7 +1309,7 @@
         <v>70</v>
       </c>
       <c r="D41" s="12">
-        <v>0.01338556457705315</v>
+        <v>0.01701271377760717</v>
       </c>
     </row>
     <row r="42" spans="2:4">
